--- a/artfynd/A 59754-2025 artfynd.xlsx
+++ b/artfynd/A 59754-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135730205</v>
       </c>
       <c r="B2" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135731041</v>
       </c>
       <c r="B3" t="n">
-        <v>44187</v>
+        <v>44189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59754-2025 artfynd.xlsx
+++ b/artfynd/A 59754-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135730205</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135731041</v>
       </c>
       <c r="B3" t="n">
-        <v>44189</v>
+        <v>44190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59754-2025 artfynd.xlsx
+++ b/artfynd/A 59754-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135730205</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59754-2025 artfynd.xlsx
+++ b/artfynd/A 59754-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135730205</v>
       </c>
       <c r="B2" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
